--- a/TEST/勤怠/勤怠_テスト04.xlsx
+++ b/TEST/勤怠/勤怠_テスト04.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\TEST\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D449ACE7-85C4-4389-BCF5-4C545D51A7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117093B3-A031-4DFB-BC36-075C37A133D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="5460" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
